--- a/evaluation_scores.xlsx
+++ b/evaluation_scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\ECEN743-SP25_Final_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFE20CE-C4FA-4175-BA7A-C03EF9B83CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4716711-FEDD-4A0A-8220-C11D71479FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D9342F0-2854-46C1-9118-B09D887AD7F4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Accuracy (MMLU Physics)</t>
   </si>
@@ -56,13 +56,22 @@
     <t>BLEU (XSum Summarization)</t>
   </si>
   <si>
-    <t>model</t>
-  </si>
-  <si>
-    <t>HUMANLY</t>
-  </si>
-  <si>
-    <t>DPO_LLAMA</t>
+    <t>SFT-Reddit</t>
+  </si>
+  <si>
+    <t>STF- General</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>STF- General + DPO-Orca</t>
+  </si>
+  <si>
+    <t>SFT-Reddit + DPO-Gutenberg</t>
+  </si>
+  <si>
+    <t>Confident</t>
   </si>
 </sst>
 </file>
@@ -86,7 +95,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -94,12 +103,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,9 +459,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA9C90B-0359-4D4D-B9EB-BC9066D564EE}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
@@ -445,118 +471,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0.2</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>9.2944059961216699E-2</v>
-      </c>
-      <c r="E2">
-        <v>2.3407209473581402E-2</v>
-      </c>
-      <c r="F2">
-        <v>5.8898228230084899E-2</v>
-      </c>
-      <c r="G2">
-        <v>3.4823415377521101E-3</v>
+      <c r="D2" s="1">
+        <v>9.2946662516394496E-2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2.3577504946469399E-2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5.8597139699440699E-2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3.2489212710799299E-3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>17000</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
         <v>0.2</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0</v>
       </c>
-      <c r="D3">
-        <v>6.8499238118099104E-2</v>
-      </c>
-      <c r="E3">
-        <v>1.7553595884190198E-2</v>
-      </c>
-      <c r="F3">
-        <v>4.5406454022631403E-2</v>
-      </c>
-      <c r="G3">
-        <v>2.7688631467666599E-3</v>
+      <c r="D3" s="1">
+        <v>9.2248584754832094E-2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2.3900481834976402E-2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>5.79758972507321E-2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3.2088867000801698E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="D4">
-        <v>9.2248584754832094E-2</v>
-      </c>
-      <c r="E4">
-        <v>2.3900481834976402E-2</v>
-      </c>
-      <c r="F4">
-        <v>5.79758972507321E-2</v>
-      </c>
-      <c r="G4">
-        <v>3.2088867000801698E-3</v>
+      <c r="D4" s="1">
+        <v>6.8499238118099104E-2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.7553595884190198E-2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>4.5406454022631403E-2</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2.7688631467666599E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>30920</v>
-      </c>
-      <c r="B5">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0</v>
       </c>
-      <c r="D5">
-        <v>9.2946662516394496E-2</v>
-      </c>
-      <c r="E5">
-        <v>2.3577504946469399E-2</v>
-      </c>
-      <c r="F5">
-        <v>5.8597139699440699E-2</v>
-      </c>
-      <c r="G5">
-        <v>3.2489212710799299E-3</v>
+      <c r="D5" s="1">
+        <v>9.2944059961216699E-2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2.3407209473581402E-2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5.8898228230084899E-2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3.4823415377521101E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>9.2041193711821304E-2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2.3666306925086901E-2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5.9023391494828402E-2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3.25341087135273E-3</v>
       </c>
     </row>
   </sheetData>
